--- a/data/trans_dic/P33B_R4-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R4-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 16,86</t>
+          <t>11,71; 17,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,44; 25,55</t>
+          <t>20,59; 25,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 20,4</t>
+          <t>16,79; 20,65</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 13,95</t>
+          <t>11,02; 15,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 24,51</t>
+          <t>20,14; 24,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 18,22</t>
+          <t>16,25; 19,35</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,65; 14,69</t>
+          <t>9,38; 14,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 19,8</t>
+          <t>17,75; 23,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 16,17</t>
+          <t>14,0; 17,76</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,57; 18,52</t>
+          <t>13,94; 18,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 25,31</t>
+          <t>21,87; 26,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 21,39</t>
+          <t>18,9; 22,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,22</t>
+          <t>12,67; 15,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 22,58</t>
+          <t>21,39; 23,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 18,19</t>
+          <t>17,5; 19,13</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86968</t>
+          <t>97303</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>154495</t>
+          <t>169548</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241463</t>
+          <t>266851</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70046; 106982</t>
+          <t>80752; 120466</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137964; 172436</t>
+          <t>150749; 186715</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215310; 267072</t>
+          <t>238699; 293694</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>123738</t>
+          <t>136667</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>213764</t>
+          <t>237754</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337503</t>
+          <t>374422</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67443; 166310</t>
+          <t>115518; 161860</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>191483; 234656</t>
+          <t>215515; 260712</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218522; 391624</t>
+          <t>344130; 409832</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83488</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>138145</t>
+          <t>162991</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221633</t>
+          <t>256290</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67999; 103506</t>
+          <t>75341; 114247</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66903; 184809</t>
+          <t>144214; 186896</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>150936; 264806</t>
+          <t>226174; 286886</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>148613</t>
+          <t>160581</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>246550</t>
+          <t>270394</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>395163</t>
+          <t>430974</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>125663; 171436</t>
+          <t>137887; 184694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197951; 276533</t>
+          <t>244568; 297211</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>347550; 431815</t>
+          <t>398395; 467498</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>442807</t>
+          <t>487850</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>752955</t>
+          <t>840688</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1195762</t>
+          <t>1328538</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>340557; 491671</t>
+          <t>447367; 536492</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>619270; 825994</t>
+          <t>798390; 882710</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1026657; 1294178</t>
+          <t>1270891; 1389085</t>
         </is>
       </c>
     </row>
